--- a/workbooks/03 Shortcuts 2 - Enter and Edit.xlsx
+++ b/workbooks/03 Shortcuts 2 - Enter and Edit.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="553">
   <si>
     <t>Challenge</t>
   </si>
@@ -1896,10 +1896,22 @@
     <t>Boss F7</t>
   </si>
   <si>
+    <t>A function key, or Ctrl plus G.</t>
+  </si>
+  <si>
+    <t>CTRL+G</t>
+  </si>
+  <si>
     <t>F7</t>
   </si>
   <si>
     <t>Boss F8</t>
+  </si>
+  <si>
+    <t>Ctrl plus Page Down.</t>
+  </si>
+  <si>
+    <t>CTRL+PGDN</t>
   </si>
   <si>
     <t>F8</t>
@@ -2902,7 +2914,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2912,12 +2924,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2927,32 +2939,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2962,30 +2974,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>192</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('S2-1 Quick Entry'!$G$15:$G$45)&amp;" / 240"</f>
@@ -3000,15 +3012,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('S2-2 Clone Machine'!$G$17:$G$50)&amp;" / 270"</f>
@@ -3023,15 +3035,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('S2-3 Stamps &amp; Smart Fill'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3046,15 +3058,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3069,12 +3081,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B18" s="12" cm="1" t="str">
         <f t="array" ref="B18">(SUM('S2-1 Quick Entry'!$G$15:$G$45)+SUM('S2-2 Clone Machine'!$G$17:$G$50)+SUM('S2-3 Stamps &amp; Smart Fill'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 890"</f>
@@ -3083,19 +3095,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('S2-1 Quick Entry'!$G$15:$G$45)+SUM('S2-2 Clone Machine'!$G$17:$G$50)+SUM('S2-3 Stamps &amp; Smart Fill'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/890,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=10),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 10)","—")</f>
@@ -3104,7 +3116,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3113,7 +3125,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -3146,7 +3158,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3154,245 +3166,245 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>196</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>110</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>200</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>116</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="19.75" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>204</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>132</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19.75" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>127</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>117</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>118</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19.75" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>257</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -4636,45 +4648,48 @@
         <v>442</v>
       </c>
       <c r="B81" t="s">
-        <v>109</v>
+        <v>443</v>
       </c>
       <c r="E81" t="s">
-        <v>138</v>
+        <v>444</v>
+      </c>
+      <c r="F81" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>447</v>
       </c>
       <c r="E82" t="s">
-        <v>141</v>
+        <v>448</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B83" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B84" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B85" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E85" cm="1">
         <f t="array" ref="E85">SUM('Boss Arena'!$D$16:$D$18)</f>
@@ -4691,15 +4706,15 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B86" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B87" t="s">
         <v>127</v>
@@ -4707,26 +4722,26 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B88" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B89" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B90" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -7944,7 +7959,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7955,7 +7970,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8199,15 +8214,15 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
-        <f t="array" ref="B20">IF($C$10="OPEN","Which keys confirm an entry and move up one cell?  (from S2-1 Quick Entry)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B20">IF($C$10="OPEN","Which key opens the Go To box?  (from S1-2 Teleport)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
-        <f t="array" ref="D20">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$20,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$E$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D20">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$20,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$81:$F$81),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E20" s="22"/>
@@ -8222,10 +8237,10 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
-        <f t="array" ref="B21">IF($C$10="OPEN","Which key confirms an entry and moves one cell to the right?  (from S2-1 Quick Entry)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B21">IF($C$10="OPEN","Which keys move to the next sheet?  (from S1-2 Teleport)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C21" s="20"/>
@@ -8245,7 +8260,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8256,7 +8271,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8284,14 +8299,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In the Boss Arena select B6:B12, type READY and press Ctrl+Enter.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(IFERROR(AND('Boss Arena'!$B$6="READY",'Boss Arena'!$B$7="READY",'Boss Arena'!$B$8="READY",'Boss Arena'!$B$9="READY",'Boss Arena'!$B$10="READY",'Boss Arena'!$B$11="READY",'Boss Arena'!$B$12="READY"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8309,14 +8324,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In D6 type Street, press Alt+Enter, type City, then press Enter.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(IFERROR(EXACT('Boss Arena'!$D$6,"Street"&amp;CHAR(10)&amp;"City"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8334,14 +8349,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","C15 sums the Q1 column. Select C15:F15 and press Ctrl+R.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$D$15,'Boss Arena'!$E$15,'Boss Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$15)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$15)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$D$15),ISERROR('Boss Arena'!$E$15),ISERROR('Boss Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$15),ABS('Boss Arena'!$D$15-Key!$E$85)&lt;=1E-9*MAX(1,ABS(Key!$E$85))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$15),ABS('Boss Arena'!$E$15-Key!$F$85)&lt;=1E-9*MAX(1,ABS(Key!$F$85))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$F$15),ABS('Boss Arena'!$F$15-Key!$G$85)&lt;=1E-9*MAX(1,ABS(Key!$G$85))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUM"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$15)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUM"))))),"LOCKED")</f>
@@ -8359,14 +8374,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","Copy LIVE (C23:F23) and paste only its values into SNAPSHOT (C21) with Ctrl+Alt+V, V.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(IFERROR(AND(NOT(_xlfn.ISFORMULA('Boss Arena'!$C$21)),'Boss Arena'!$C$21=31,NOT(_xlfn.ISFORMULA('Boss Arena'!$D$21)),'Boss Arena'!$D$21=31,NOT(_xlfn.ISFORMULA('Boss Arena'!$E$21)),'Boss Arena'!$E$21=34,NOT(_xlfn.ISFORMULA('Boss Arena'!$F$21)),'Boss Arena'!$F$21=35),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8384,14 +8399,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","Select F6 and stamp today's date with Ctrl+;, then Enter.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(IFERROR(AND(ISNUMBER('Boss Arena'!$F$6),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$6)),INT('Boss Arena'!$F$6)=TODAY()),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8409,14 +8424,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In J6 type Lovelace (the last name in I6), then select J7 and press Ctrl+E.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(IFERROR(AND(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),'Boss Arena'!$J$6="Lovelace",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$7)),'Boss Arena'!$J$7="Turing",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$8)),'Boss Arena'!$J$8="Hopper",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),'Boss Arena'!$J$9="Lamarr",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),'Boss Arena'!$J$10="Torvalds",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),'Boss Arena'!$J$11="Easley"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8434,14 +8449,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","Move Nova's row (L7:N7) up one row: select it, Ctrl+X, click L6, Ctrl+V.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(IFERROR(AND(INDIRECT("'Boss Arena'!L6")="Nova",INDIRECT("'Boss Arena'!M6")=88,INDIRECT("'Boss Arena'!N6")=3,COUNTA(INDIRECT("'Boss Arena'!L7:N7"))=0),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8459,14 +8474,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","Select F9, press Alt+↓ and choose Platinum.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(IFERROR(AND('Boss Arena'!$F$9="Platinum"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>

--- a/workbooks/03 Shortcuts 2 - Enter and Edit.xlsx
+++ b/workbooks/03 Shortcuts 2 - Enter and Edit.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="554">
   <si>
     <t>Challenge</t>
   </si>
@@ -575,73 +575,76 @@
     <t>T2</t>
   </si>
   <si>
+    <t>Which move is this? Confirm the entry and move right (Shift+Tab moves left).</t>
+  </si>
+  <si>
+    <t>S2-1 Quick Entry T3</t>
+  </si>
+  <si>
+    <t>Enter plus Ctrl.</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>Which keys fill every selected cell with what you typed?</t>
+  </si>
+  <si>
+    <t>S2-1 Quick Entry T4</t>
+  </si>
+  <si>
+    <t>Enter plus Alt.</t>
+  </si>
+  <si>
+    <t>Ctrl+;</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>Which keys start a new line inside the same cell?</t>
+  </si>
+  <si>
+    <t>S2-1 Quick Entry T5</t>
+  </si>
+  <si>
+    <t>The top-left key.</t>
+  </si>
+  <si>
+    <t>Ctrl+Y</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Which key cancels an entry and leaves the cell unchanged?</t>
+  </si>
+  <si>
+    <t>CHALLENGES · recall it, then do it</t>
+  </si>
+  <si>
+    <t>▶ Open S2-1 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>S2-1 Quick Entry C1</t>
+  </si>
+  <si>
+    <t>SHIFT+ENTER</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>S2-1 Quick Entry C2</t>
+  </si>
+  <si>
+    <t>TAB</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
     <t>Which key confirms an entry and moves one cell to the right?</t>
-  </si>
-  <si>
-    <t>S2-1 Quick Entry T3</t>
-  </si>
-  <si>
-    <t>Enter plus Ctrl.</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>Which keys fill every selected cell with what you typed?</t>
-  </si>
-  <si>
-    <t>S2-1 Quick Entry T4</t>
-  </si>
-  <si>
-    <t>Enter plus Alt.</t>
-  </si>
-  <si>
-    <t>Ctrl+;</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>Which keys start a new line inside the same cell?</t>
-  </si>
-  <si>
-    <t>S2-1 Quick Entry T5</t>
-  </si>
-  <si>
-    <t>The top-left key.</t>
-  </si>
-  <si>
-    <t>Ctrl+Y</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Which key cancels an entry and leaves the cell unchanged?</t>
-  </si>
-  <si>
-    <t>CHALLENGES · recall it, then do it</t>
-  </si>
-  <si>
-    <t>▶ Open S2-1 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>S2-1 Quick Entry C1</t>
-  </si>
-  <si>
-    <t>SHIFT+ENTER</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>S2-1 Quick Entry C2</t>
-  </si>
-  <si>
-    <t>TAB</t>
-  </si>
-  <si>
-    <t>C2</t>
   </si>
   <si>
     <t>S2-1 Quick Entry C3</t>
@@ -2914,7 +2917,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2924,12 +2927,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2939,32 +2942,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2974,30 +2977,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('S2-1 Quick Entry'!$G$15:$G$45)&amp;" / 240"</f>
@@ -3012,15 +3015,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('S2-2 Clone Machine'!$G$17:$G$50)&amp;" / 270"</f>
@@ -3035,15 +3038,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('S2-3 Stamps &amp; Smart Fill'!$G$14:$G$42)&amp;" / 220"</f>
@@ -3058,15 +3061,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3081,12 +3084,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B18" s="12" cm="1" t="str">
         <f t="array" ref="B18">(SUM('S2-1 Quick Entry'!$G$15:$G$45)+SUM('S2-2 Clone Machine'!$G$17:$G$50)+SUM('S2-3 Stamps &amp; Smart Fill'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))&amp;" / 890"</f>
@@ -3095,19 +3098,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('S2-1 Quick Entry'!$G$15:$G$45)+SUM('S2-2 Clone Machine'!$G$17:$G$50)+SUM('S2-3 Stamps &amp; Smart Fill'!$G$14:$G$42)+SUM(Boss!$G$14:$G$33))/890,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=10),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 10)","—")</f>
@@ -3116,7 +3119,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3125,7 +3128,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -3158,7 +3161,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3166,245 +3169,245 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>25</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="35.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>110</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="35.5" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>116</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="19.75" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>132</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19.75" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>127</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>117</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>118</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19.75" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -3739,72 +3742,72 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s">
         <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
         <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s">
         <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s">
         <v>109</v>
@@ -3815,7 +3818,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B27" t="s">
         <v>115</v>
@@ -3826,146 +3829,146 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s">
         <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B29" t="s">
         <v>126</v>
       </c>
       <c r="E29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B30" t="s">
         <v>131</v>
       </c>
       <c r="E30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E31" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F31" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H31" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I31" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F32" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G32" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H32" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I32" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J32" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B33" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E33" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G33" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E34" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B35" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E35" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E36" t="s">
         <v>110</v>
@@ -3974,7 +3977,7 @@
         <v>132</v>
       </c>
       <c r="G36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
@@ -3982,10 +3985,10 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C37" t="s">
         <v>111</v>
@@ -4000,15 +4003,15 @@
         <v>117</v>
       </c>
       <c r="H37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B38" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C38" t="s">
         <v>110</v>
@@ -4020,7 +4023,7 @@
         <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H38" t="s">
         <v>25</v>
@@ -4028,42 +4031,42 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G39" t="s">
         <v>116</v>
       </c>
       <c r="H39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C40" t="s">
         <v>116</v>
       </c>
       <c r="E40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G40" t="s">
         <v>116</v>
@@ -4074,16 +4077,16 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B41" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F41" t="s">
         <v>117</v>
@@ -4097,16 +4100,16 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C42" t="s">
         <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F42" t="s">
         <v>111</v>
@@ -4120,90 +4123,90 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B45" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E46" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E47" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E48" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E49" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E50" cm="1">
         <f t="array" ref="E50">SUM('S2-2 Arena'!$D$7:$D$10)</f>
@@ -4228,134 +4231,134 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B51" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B52" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E54" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B56" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E56" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F56" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E57" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B59" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E60" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F60" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G60" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E61" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s">
         <v>115</v>
@@ -4366,22 +4369,22 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C63" t="s">
         <v>127</v>
       </c>
       <c r="E63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F63" t="s">
         <v>127</v>
       </c>
       <c r="G63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H63" t="s">
         <v>132</v>
@@ -4389,16 +4392,16 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B64" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C64" t="s">
         <v>117</v>
       </c>
       <c r="E64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F64" t="s">
         <v>117</v>
@@ -4407,15 +4410,15 @@
         <v>116</v>
       </c>
       <c r="H64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B65" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C65" t="s">
         <v>118</v>
@@ -4427,7 +4430,7 @@
         <v>118</v>
       </c>
       <c r="G65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H65" t="s">
         <v>22</v>
@@ -4435,16 +4438,16 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C66" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E66" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F66" t="s">
         <v>110</v>
@@ -4453,243 +4456,243 @@
         <v>25</v>
       </c>
       <c r="H66" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E67" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F67" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B68" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E68" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F68" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G68" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H68" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I68" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J68" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K68" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B69" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E69" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B70" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E70" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B71" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B73" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B74" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B75" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E75" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F75" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B76" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E76" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F76" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G76" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H76" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I76" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J76" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K76" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B77" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E77" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B78" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E78" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B79" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E79" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F79" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B80" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E80" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B81" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E81" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F81" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B82" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E82" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B83" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B84" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B85" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E85" cm="1">
         <f t="array" ref="E85">SUM('Boss Arena'!$D$16:$D$18)</f>
@@ -4706,15 +4709,15 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B86" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B87" t="s">
         <v>127</v>
@@ -4722,26 +4725,26 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B88" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B89" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B90" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -4769,7 +4772,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4780,7 +4783,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -5346,7 +5349,7 @@
         <v>142</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -5365,7 +5368,7 @@
     </row>
     <row r="39" spans="1:7" ht="35.5" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>124</v>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="40" spans="1:7" ht="35.5" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>129</v>
@@ -5409,7 +5412,7 @@
     </row>
     <row r="41" spans="1:7" ht="35.5" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>134</v>
@@ -5431,13 +5434,13 @@
     </row>
     <row r="42" spans="1:7" ht="51.25" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(IFERROR(AND('S2-1 Arena'!$B$6="DONE",'S2-1 Arena'!$B$7="DONE",'S2-1 Arena'!$B$8="DONE",'S2-1 Arena'!$B$9="DONE",'S2-1 Arena'!$B$10="DONE",'S2-1 Arena'!$B$11="DONE",'S2-1 Arena'!$B$12="DONE",'S2-1 Arena'!$B$13="DONE",'S2-1 Arena'!$B$14="DONE",'S2-1 Arena'!$B$15="DONE"),FALSE),"✔ CLEAR","· not yet")</f>
@@ -5455,13 +5458,13 @@
     </row>
     <row r="43" spans="1:7" ht="35.5" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D43" s="21" cm="1" t="str">
         <f t="array" ref="D43">IF(IFERROR(EXACT('S2-1 Arena'!$D$6,"Line 1"&amp;CHAR(10)&amp;"Line 2"),FALSE),"✔ CLEAR","· not yet")</f>
@@ -5479,13 +5482,13 @@
     </row>
     <row r="44" spans="1:7" ht="35.5" customHeight="1">
       <c r="A44" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D44" s="21" cm="1" t="str">
         <f t="array" ref="D44">IF(IFERROR(AND('S2-1 Arena'!$F$6="Name",'S2-1 Arena'!$G$6="Score",'S2-1 Arena'!$H$6="Level"),FALSE),"✔ CLEAR","· not yet")</f>
@@ -5503,13 +5506,13 @@
     </row>
     <row r="45" spans="1:7" ht="35.5" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D45" s="21" cm="1" t="str">
         <f t="array" ref="D45">IF(IFERROR(AND('S2-1 Arena'!$F$12="Bottom",'S2-1 Arena'!$F$11="Top"),FALSE),"✔ CLEAR","· not yet")</f>
@@ -5764,7 +5767,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5775,7 +5778,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -5827,10 +5830,10 @@
         <v>17</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="35.5" customHeight="1">
@@ -5838,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>111</v>
@@ -5849,7 +5852,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>110</v>
@@ -5860,10 +5863,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="51.25" customHeight="1">
@@ -5871,7 +5874,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>116</v>
@@ -5879,21 +5882,21 @@
     </row>
     <row r="12" spans="1:7" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="51.25" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>132</v>
@@ -5938,7 +5941,7 @@
         <v>46</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -5960,7 +5963,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -5982,7 +5985,7 @@
         <v>66</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -6004,7 +6007,7 @@
         <v>71</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -6026,7 +6029,7 @@
         <v>76</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -6048,7 +6051,7 @@
         <v>81</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -6070,7 +6073,7 @@
         <v>86</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -6092,7 +6095,7 @@
         <v>91</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="21" cm="1" t="str">
@@ -6114,7 +6117,7 @@
         <v>100</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -6136,7 +6139,7 @@
         <v>105</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -6192,7 +6195,7 @@
         <v>112</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -6214,7 +6217,7 @@
         <v>119</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -6236,7 +6239,7 @@
         <v>123</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -6258,7 +6261,7 @@
         <v>128</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -6280,7 +6283,7 @@
         <v>133</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -6299,10 +6302,10 @@
     </row>
     <row r="35" spans="1:7" ht="19.75" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -6321,10 +6324,10 @@
     </row>
     <row r="36" spans="1:7" ht="19.75" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -6354,7 +6357,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="B39" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6385,7 +6388,7 @@
         <v>139</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="21" cm="1" t="str">
@@ -6407,7 +6410,7 @@
         <v>142</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21" cm="1" t="str">
@@ -6426,10 +6429,10 @@
     </row>
     <row r="43" spans="1:7" ht="19.75" customHeight="1">
       <c r="A43" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="21" cm="1" t="str">
@@ -6448,10 +6451,10 @@
     </row>
     <row r="44" spans="1:7" ht="19.75" customHeight="1">
       <c r="A44" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="21" cm="1" t="str">
@@ -6470,10 +6473,10 @@
     </row>
     <row r="45" spans="1:7" ht="35.5" customHeight="1">
       <c r="A45" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21" cm="1" t="str">
@@ -6492,10 +6495,10 @@
     </row>
     <row r="46" spans="1:7" ht="19.75" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="21" cm="1" t="str">
@@ -6514,10 +6517,10 @@
     </row>
     <row r="47" spans="1:7" ht="19.75" customHeight="1">
       <c r="A47" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21" cm="1" t="str">
@@ -6536,13 +6539,13 @@
     </row>
     <row r="48" spans="1:7" ht="35.5" customHeight="1">
       <c r="A48" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D48" s="21" cm="1" t="str">
         <f t="array" ref="D48">IF(COUNTA('S2-2 Arena'!$D$6,'S2-2 Arena'!$E$6,'S2-2 Arena'!$F$6,'S2-2 Arena'!$G$6,'S2-2 Arena'!$H$6)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('S2-2 Arena'!$D$6)),NOT(_xlfn.ISFORMULA('S2-2 Arena'!$E$6)),NOT(_xlfn.ISFORMULA('S2-2 Arena'!$F$6)),NOT(_xlfn.ISFORMULA('S2-2 Arena'!$G$6)),NOT(_xlfn.ISFORMULA('S2-2 Arena'!$H$6))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('S2-2 Arena'!$D$6),ISERROR('S2-2 Arena'!$E$6),ISERROR('S2-2 Arena'!$F$6),ISERROR('S2-2 Arena'!$G$6),ISERROR('S2-2 Arena'!$H$6)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('S2-2 Arena'!$D$6),ABS('S2-2 Arena'!$D$6-Key!$E$50)&lt;=1E-9*MAX(1,ABS(Key!$E$50))),FALSE),IFERROR(AND(ISNUMBER('S2-2 Arena'!$E$6),ABS('S2-2 Arena'!$E$6-Key!$F$50)&lt;=1E-9*MAX(1,ABS(Key!$F$50))),FALSE),IFERROR(AND(ISNUMBER('S2-2 Arena'!$F$6),ABS('S2-2 Arena'!$F$6-Key!$G$50)&lt;=1E-9*MAX(1,ABS(Key!$G$50))),FALSE),IFERROR(AND(ISNUMBER('S2-2 Arena'!$G$6),ABS('S2-2 Arena'!$G$6-Key!$H$50)&lt;=1E-9*MAX(1,ABS(Key!$H$50))),FALSE),IFERROR(AND(ISNUMBER('S2-2 Arena'!$H$6),ABS('S2-2 Arena'!$H$6-Key!$I$50)&lt;=1E-9*MAX(1,ABS(Key!$I$50))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUM"&amp;"(",UPPER(_xlfn.FORMULATEXT('S2-2 Arena'!$D$6)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUM")))))</f>
@@ -6560,13 +6563,13 @@
     </row>
     <row r="49" spans="1:7" ht="67" customHeight="1">
       <c r="A49" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D49" s="21" cm="1" t="str">
         <f t="array" ref="D49">IF(IFERROR(AND(NOT(_xlfn.ISFORMULA('S2-2 Arena'!$C$13)),'S2-2 Arena'!$C$13=980,NOT(_xlfn.ISFORMULA('S2-2 Arena'!$D$13)),'S2-2 Arena'!$D$13=1020,NOT(_xlfn.ISFORMULA('S2-2 Arena'!$E$13)),'S2-2 Arena'!$E$13=1270,NOT(_xlfn.ISFORMULA('S2-2 Arena'!$F$13)),'S2-2 Arena'!$F$13=1030,NOT(_xlfn.ISFORMULA('S2-2 Arena'!$G$13)),'S2-2 Arena'!$G$13=1530,NOT(_xlfn.ISFORMULA('S2-2 Arena'!$H$13)),'S2-2 Arena'!$H$13=1035),FALSE),"✔ CLEAR","· not yet")</f>
@@ -6584,13 +6587,13 @@
     </row>
     <row r="50" spans="1:7" ht="51.25" customHeight="1">
       <c r="A50" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D50" s="21" cm="1" t="str">
         <f t="array" ref="D50">IF(IFERROR(AND(INDIRECT("'S2-2 Arena'!B21")="Zelda",INDIRECT("'S2-2 Arena'!C21")=980,INDIRECT("'S2-2 Arena'!D21")=1,COUNTA(INDIRECT("'S2-2 Arena'!B22:D22"))=0),FALSE),"✔ CLEAR","· not yet")</f>
@@ -6762,7 +6765,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6775,38 +6778,38 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" s="5" cm="1">
         <f t="array" ref="C6">SUM(C7:C10)</f>
@@ -6820,7 +6823,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C7" s="5">
         <v>120</v>
@@ -6843,7 +6846,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C8" s="5">
         <v>800</v>
@@ -6866,7 +6869,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C9" s="5">
         <v>60</v>
@@ -6889,7 +6892,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C10" s="5">
         <v>0</v>
@@ -6912,7 +6915,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
@@ -6923,7 +6926,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="5" cm="1">
         <f t="array" ref="C15">SUM(C7:C10)</f>
@@ -6952,18 +6955,18 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="27" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C22" s="5">
         <v>980</v>
@@ -7000,7 +7003,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7011,7 +7014,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7063,7 +7066,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>127</v>
@@ -7074,7 +7077,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>117</v>
@@ -7085,7 +7088,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>118</v>
@@ -7096,10 +7099,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
@@ -7141,7 +7144,7 @@
         <v>46</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="21" cm="1" t="str">
@@ -7163,7 +7166,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="21" cm="1" t="str">
@@ -7185,7 +7188,7 @@
         <v>66</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="21" cm="1" t="str">
@@ -7207,7 +7210,7 @@
         <v>71</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -7229,7 +7232,7 @@
         <v>76</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -7251,7 +7254,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -7273,7 +7276,7 @@
         <v>86</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -7295,7 +7298,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -7317,7 +7320,7 @@
         <v>100</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -7339,7 +7342,7 @@
         <v>105</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -7395,7 +7398,7 @@
         <v>112</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -7417,7 +7420,7 @@
         <v>119</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -7439,7 +7442,7 @@
         <v>123</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -7461,7 +7464,7 @@
         <v>128</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -7491,7 +7494,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7522,7 +7525,7 @@
         <v>139</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -7544,7 +7547,7 @@
         <v>142</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -7563,10 +7566,10 @@
     </row>
     <row r="37" spans="1:7" ht="19.75" customHeight="1">
       <c r="A37" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -7585,10 +7588,10 @@
     </row>
     <row r="38" spans="1:7" ht="19.75" customHeight="1">
       <c r="A38" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -7607,16 +7610,16 @@
     </row>
     <row r="39" spans="1:7" ht="51.25" customHeight="1">
       <c r="A39" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D39" s="21" cm="1" t="str">
-        <f t="array" ref="D39">IF(IFERROR(AND(ISNUMBER('S2-3 Arena'!$C$6),NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$6)),INT('S2-3 Arena'!$C$6)=TODAY()),FALSE),"✔ CLEAR","· not yet")</f>
+        <f t="array" ref="D39">IF(IFERROR(AND(ISNUMBER('S2-3 Arena'!$C$6),NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$6)),'S2-3 Arena'!$C$6=INT('S2-3 Arena'!$C$6),'S2-3 Arena'!$C$6&gt;=DATE(2026,10,12),'S2-3 Arena'!$C$6&lt;=TODAY()),FALSE),"✔ CLEAR","· not yet")</f>
         <v>· not yet</v>
       </c>
       <c r="E39" s="22"/>
@@ -7631,13 +7634,13 @@
     </row>
     <row r="40" spans="1:7" ht="19.75" customHeight="1">
       <c r="A40" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D40" s="21" cm="1" t="str">
         <f t="array" ref="D40">IF(IFERROR(AND(ISNUMBER('S2-3 Arena'!$C$8),NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$8)),'S2-3 Arena'!$C$8&gt;0,'S2-3 Arena'!$C$8&lt;1),FALSE),"✔ CLEAR","· not yet")</f>
@@ -7655,13 +7658,13 @@
     </row>
     <row r="41" spans="1:7" ht="51.25" customHeight="1">
       <c r="A41" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D41" s="21" cm="1" t="str">
         <f t="array" ref="D41">IF(IFERROR(AND(NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$12)),'S2-3 Arena'!$C$12="Ada",NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$13)),'S2-3 Arena'!$C$13="Alan",NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$14)),'S2-3 Arena'!$C$14="Grace",NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$15)),'S2-3 Arena'!$C$15="Katherine",NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$16)),'S2-3 Arena'!$C$16="Tim",NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$17)),'S2-3 Arena'!$C$17="Margaret",NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$18)),'S2-3 Arena'!$C$18="Linus",NOT(_xlfn.ISFORMULA('S2-3 Arena'!$C$19)),'S2-3 Arena'!$C$19="Hedy"),FALSE),"✔ CLEAR","· not yet")</f>
@@ -7679,13 +7682,13 @@
     </row>
     <row r="42" spans="1:7" ht="35.5" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
         <f t="array" ref="D42">IF(IFERROR(AND('S2-3 Arena'!$C$22="Gold"),FALSE),"✔ CLEAR","· not yet")</f>
@@ -7833,7 +7836,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7846,83 +7849,83 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C6" s="29"/>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C8" s="30"/>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C12" s="28"/>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C14" s="28"/>
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C16" s="28"/>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C17" s="28"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C18" s="28"/>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C19" s="28"/>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C22" s="28"/>
     </row>
@@ -7959,7 +7962,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7970,7 +7973,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7989,7 +7992,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -8000,19 +8003,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C8" s="31" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -8021,7 +8024,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C9" s="31">
         <v>10</v>
@@ -8029,7 +8032,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('S2-1 Quick Entry'!$G$15:$G$45)&gt;=240*0.5,SUM('S2-2 Clone Machine'!$G$17:$G$50)&gt;=270*0.5,SUM('S2-3 Stamps &amp; Smart Fill'!$G$14:$G$42)&gt;=220*0.5),"OPEN","LOCKED")</f>
@@ -8042,7 +8045,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -8076,7 +8079,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B14" s="32" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which keys type today's date as a fixed value?  (from S2-3 Stamps &amp; Smart Fill)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8099,7 +8102,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B15" s="32" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which keys type the current time as a fixed value?  (from S2-3 Stamps &amp; Smart Fill)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8122,7 +8125,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B16" s="32" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which keys run Flash Fill?  (from S2-3 Stamps &amp; Smart Fill)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8168,7 +8171,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B18" s="32" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which keys insert a function's argument names after you type its name?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8191,7 +8194,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B19" s="32" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which keys open the Insert Function dialog?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8214,7 +8217,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B20" s="32" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which key opens the Go To box?  (from S1-2 Teleport)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8237,7 +8240,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B21" s="32" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which keys move to the next sheet?  (from S1-2 Teleport)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8260,7 +8263,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8271,7 +8274,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8299,14 +8302,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B26" s="32" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In the Boss Arena select B6:B12, type READY and press Ctrl+Enter.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(IFERROR(AND('Boss Arena'!$B$6="READY",'Boss Arena'!$B$7="READY",'Boss Arena'!$B$8="READY",'Boss Arena'!$B$9="READY",'Boss Arena'!$B$10="READY",'Boss Arena'!$B$11="READY",'Boss Arena'!$B$12="READY"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8324,14 +8327,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B27" s="32" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","In D6 type Street, press Alt+Enter, type City, then press Enter.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(IFERROR(EXACT('Boss Arena'!$D$6,"Street"&amp;CHAR(10)&amp;"City"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8349,14 +8352,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B28" s="32" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","C15 sums the Q1 column. Select C15:F15 and press Ctrl+R.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(COUNTA('Boss Arena'!$D$15,'Boss Arena'!$E$15,'Boss Arena'!$F$15)=0,"",IF(OR(NOT(_xlfn.ISFORMULA('Boss Arena'!$D$15)),NOT(_xlfn.ISFORMULA('Boss Arena'!$E$15)),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$15))),"✘ Some cells aren't formulas yet",IF(OR(ISERROR('Boss Arena'!$D$15),ISERROR('Boss Arena'!$E$15),ISERROR('Boss Arena'!$F$15)),"✘ Some cells show an error",IF(NOT(AND(IFERROR(AND(ISNUMBER('Boss Arena'!$D$15),ABS('Boss Arena'!$D$15-Key!$E$85)&lt;=1E-9*MAX(1,ABS(Key!$E$85))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$E$15),ABS('Boss Arena'!$E$15-Key!$F$85)&lt;=1E-9*MAX(1,ABS(Key!$F$85))),FALSE),IFERROR(AND(ISNUMBER('Boss Arena'!$F$15),ABS('Boss Arena'!$F$15-Key!$G$85)&lt;=1E-9*MAX(1,ABS(Key!$G$85))),FALSE))),"✘ TRY AGAIN",IF(AND(OR(ISNUMBER(FIND({"=","(",",","+","-","*","/","&amp;"," ","&lt;","&gt;",":","@","^"}&amp;"SUM"&amp;"(",UPPER(_xlfn.FORMULATEXT('Boss Arena'!$D$15)))))),"✔ CLEAR","✘ CLOSE · right value, but use SUM"))))),"LOCKED")</f>
@@ -8374,14 +8377,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B29" s="32" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","Copy LIVE (C23:F23) and paste only its values into SNAPSHOT (C21) with Ctrl+Alt+V, V.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(IFERROR(AND(NOT(_xlfn.ISFORMULA('Boss Arena'!$C$21)),'Boss Arena'!$C$21=31,NOT(_xlfn.ISFORMULA('Boss Arena'!$D$21)),'Boss Arena'!$D$21=31,NOT(_xlfn.ISFORMULA('Boss Arena'!$E$21)),'Boss Arena'!$E$21=34,NOT(_xlfn.ISFORMULA('Boss Arena'!$F$21)),'Boss Arena'!$F$21=35),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8399,17 +8402,17 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B30" s="32" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","Select F6 and stamp today's date with Ctrl+;, then Enter.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
-        <f t="array" ref="D30">IF($C$10="OPEN",IF(IFERROR(AND(ISNUMBER('Boss Arena'!$F$6),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$6)),INT('Boss Arena'!$F$6)=TODAY()),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
+        <f t="array" ref="D30">IF($C$10="OPEN",IF(IFERROR(AND(ISNUMBER('Boss Arena'!$F$6),NOT(_xlfn.ISFORMULA('Boss Arena'!$F$6)),'Boss Arena'!$F$6=INT('Boss Arena'!$F$6),'Boss Arena'!$F$6&gt;=DATE(2026,10,12),'Boss Arena'!$F$6&lt;=TODAY()),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E30" s="22"/>
@@ -8424,14 +8427,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B31" s="32" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","In J6 type Lovelace (the last name in I6), then select J7 and press Ctrl+E.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(IFERROR(AND(NOT(_xlfn.ISFORMULA('Boss Arena'!$J$6)),'Boss Arena'!$J$6="Lovelace",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$7)),'Boss Arena'!$J$7="Turing",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$8)),'Boss Arena'!$J$8="Hopper",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$9)),'Boss Arena'!$J$9="Lamarr",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$10)),'Boss Arena'!$J$10="Torvalds",NOT(_xlfn.ISFORMULA('Boss Arena'!$J$11)),'Boss Arena'!$J$11="Easley"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8449,14 +8452,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B32" s="32" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","Move Nova's row (L7:N7) up one row: select it, Ctrl+X, click L6, Ctrl+V.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(IFERROR(AND(INDIRECT("'Boss Arena'!L6")="Nova",INDIRECT("'Boss Arena'!M6")=88,INDIRECT("'Boss Arena'!N6")=3,COUNTA(INDIRECT("'Boss Arena'!L7:N7"))=0),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8474,14 +8477,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B33" s="32" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","Select F9, press Alt+↓ and choose Platinum.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(IFERROR(AND('Boss Arena'!$F$9="Platinum"),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -8602,7 +8605,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -8615,36 +8618,36 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="B5" s="27" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N5" s="27" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8652,18 +8655,18 @@
       <c r="D6" s="28"/>
       <c r="F6" s="29"/>
       <c r="I6" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J6" s="28"/>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="28"/>
       <c r="I7" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J7" s="28"/>
       <c r="L7" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M7" s="5">
         <v>88</v>
@@ -8675,10 +8678,10 @@
     <row r="8" spans="1:14">
       <c r="B8" s="28"/>
       <c r="F8" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J8" s="28"/>
     </row>
@@ -8686,21 +8689,21 @@
       <c r="B9" s="28"/>
       <c r="F9" s="28"/>
       <c r="I9" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J9" s="28"/>
     </row>
     <row r="10" spans="1:14">
       <c r="B10" s="28"/>
       <c r="I10" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J10" s="28"/>
     </row>
     <row r="11" spans="1:14">
       <c r="B11" s="28"/>
       <c r="I11" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J11" s="28"/>
     </row>
@@ -8709,24 +8712,24 @@
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="27" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" s="5" cm="1">
         <f t="array" ref="C15">SUM(C16:C18)</f>
@@ -8738,7 +8741,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C16" s="5">
         <v>10</v>
@@ -8755,7 +8758,7 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C17" s="5">
         <v>8</v>
@@ -8772,7 +8775,7 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C18" s="5">
         <v>13</v>
@@ -8789,7 +8792,7 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
@@ -8798,7 +8801,7 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C23" s="5" cm="1">
         <f t="array" ref="C23">SUM(C16:C18)</f>

--- a/workbooks/03 Shortcuts 2 - Enter and Edit.xlsx
+++ b/workbooks/03 Shortcuts 2 - Enter and Edit.xlsx
@@ -2118,7 +2118,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ ENTER &amp; EDIT</t>
@@ -3122,7 +3122,7 @@
         <v>516</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
-        <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Start!$E$16="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>S2-1 Quick Entry</v>
       </c>
     </row>
